--- a/wwwroot/template/TemplateHistoryV2.xlsx
+++ b/wwwroot/template/TemplateHistoryV2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khanhmf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{811BEF5A-F7DB-4D67-ADD2-EA80D6CB903A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6F68B981-1440-4B33-98B5-BA119A42A137}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{6F68B981-1440-4B33-98B5-BA119A42A137}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -199,13 +199,17 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -220,10 +224,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,134 +561,139 @@
   <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="9"/>
-    <col min="2" max="2" width="15.140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="15" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="15" style="9" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="9" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" style="9" customWidth="1"/>
-    <col min="13" max="19" width="9.140625" style="9"/>
-    <col min="20" max="20" width="16.140625" style="9" customWidth="1"/>
-    <col min="21" max="21" width="18.5703125" style="9" customWidth="1"/>
-    <col min="22" max="22" width="22.5703125" style="9" customWidth="1"/>
-    <col min="23" max="23" width="22.7109375" style="9" customWidth="1"/>
-    <col min="24" max="24" width="18.7109375" style="9" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="15.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15" style="4" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" style="4" customWidth="1"/>
+    <col min="13" max="19" width="9.140625" style="4"/>
+    <col min="20" max="20" width="16.140625" style="4" customWidth="1"/>
+    <col min="21" max="21" width="18.5703125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="22.5703125" style="4" customWidth="1"/>
+    <col min="23" max="23" width="22.7109375" style="4" customWidth="1"/>
+    <col min="24" max="24" width="18.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="3" t="s">
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="4" t="s">
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="5" t="s">
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="6" t="s">
+    <row r="2" spans="1:24" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="T2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="V2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="5"/>
+      <c r="X2" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="U1:W1"/>
@@ -699,11 +704,6 @@
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:P1"/>
     <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
